--- a/r5-aist-trustworthyai-poc-pipeline/ValueSet-gdpr-art9-exception-vs.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/ValueSet-gdpr-art9-exception-vs.xlsx
@@ -42,13 +42,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>GDPR Art 9 Exception for AI Health Data</t>
+    <t>GDPR Article 9 Exception ValueSet</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
